--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46016.875</v>
+        <v>46016.64583333334</v>
       </c>
     </row>
     <row r="12">
@@ -1823,101 +1823,220 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>46016.875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>JS Saoura</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>El Bayadh</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="3" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>46016.875</v>
       </c>
     </row>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46016.49305555555</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
         <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
         <v>1.33</v>
@@ -1501,64 +1501,64 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
         <v>2.7</v>
@@ -1138,10 +1138,10 @@
         <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P7" t="n">
         <v>2.15</v>
@@ -1302,7 +1302,7 @@
         <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC7" t="n">
         <v>3.41</v>
@@ -1501,64 +1501,64 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="P9" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.61</v>
+        <v>6.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
         <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="N4" t="n">
         <v>2.7</v>
@@ -1138,10 +1138,10 @@
         <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>2.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
         <v>4.9</v>
@@ -1290,7 +1290,7 @@
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
         <v>1.27</v>
@@ -1299,7 +1299,7 @@
         <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
         <v>1.74</v>
@@ -1317,7 +1317,7 @@
         <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
         <v>1.84</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1800,244 +1800,6 @@
       </c>
       <c r="AI11" s="3" t="n">
         <v>46016.64583333334</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46016</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>USM Khenchela</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CS Constantine</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="3" t="n">
-        <v>46016.875</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46016</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>JS Saoura</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3" t="n">
-        <v>46016.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.85</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.85</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="N8" t="n">
         <v>3.3</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
         <v>3</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.85</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
         <v>5.8</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
         <v>2.14</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M6" t="n">
         <v>2.75</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.85</v>
-      </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46016.45833333334</v>
@@ -1254,70 +1254,70 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
         <v>2.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
         <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
         <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
         <v>1.74</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
         <v>1.84</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.1</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.19</v>
+        <v>7.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.85</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
         <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
         <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46016.64583333334</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>7.92</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>3.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.75</v>
+        <v>3.39</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.05</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>3.39</v>
+        <v>4.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>3.24</v>
@@ -936,16 +936,16 @@
         <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC4" t="n">
         <v>7.1</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
         <v>3.37</v>
@@ -1174,10 +1174,10 @@
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
         <v>3.08</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.05</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>3.39</v>
+        <v>4.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>7.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.75</v>
+        <v>3.39</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
         <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.98</v>
+        <v>6.87</v>
       </c>
       <c r="R11" t="n">
         <v>1.55</v>
@@ -1754,13 +1754,13 @@
         <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V11" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
         <v>1.04</v>
@@ -1772,31 +1772,31 @@
         <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AB11" t="n">
         <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AD11" t="n">
         <v>1.12</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46016.64583333334</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="M2" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.72</v>
+        <v>3.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>10.5</v>
+        <v>7.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.13</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE3" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>
@@ -1025,34 +1025,34 @@
         <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
         <v>1.56</v>
@@ -1061,28 +1061,28 @@
         <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
         <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46016.41666666666</v>
@@ -1180,10 +1180,10 @@
         <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
         <v>6.7</v>
@@ -1257,19 +1257,19 @@
         <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="P7" t="n">
         <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -1302,13 +1302,13 @@
         <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE7" t="n">
         <v>1.8</v>
@@ -1382,34 +1382,34 @@
         <v>7.92</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
         <v>1.65</v>
@@ -1418,28 +1418,28 @@
         <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46016.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.39</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>6.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1775,10 +1775,10 @@
         <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
         <v>4.65</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>4.06</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.25</v>
       </c>
-      <c r="V3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AC3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC4" t="n">
         <v>4.55</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AD4" t="n">
         <v>1.13</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>4.45</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>6.3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>6.3</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC3" t="n">
         <v>4.55</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AD3" t="n">
         <v>1.13</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE3" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="N4" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>4.06</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AA4" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.25</v>
       </c>
-      <c r="V4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AC4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N2" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>2.87</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="M3" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>4.06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>3.34</v>
@@ -817,7 +817,7 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
         <v>2.56</v>
@@ -829,19 +829,19 @@
         <v>1.51</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
         <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
         <v>1.28</v>
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="M5" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="O5" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.34</v>
+        <v>5.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
         <v>9.1</v>
@@ -1052,37 +1052,37 @@
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46016.41666666666</v>
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>2.29</v>
       </c>
       <c r="M8" t="n">
-        <v>3.32</v>
+        <v>2.71</v>
       </c>
       <c r="N8" t="n">
-        <v>7.92</v>
+        <v>3.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
         <v>10</v>
@@ -1415,31 +1415,31 @@
         <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="AD8" t="n">
         <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46016.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="N9" t="n">
-        <v>6.3</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>6.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="M2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O2" t="n">
         <v>2.87</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -906,25 +906,25 @@
         <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
         <v>4.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="T4" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="V4" t="n">
         <v>10.5</v>
@@ -933,7 +933,7 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Y4" t="n">
         <v>1.83</v>
@@ -948,19 +948,19 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
         <v>1.47</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="N5" t="n">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>2.69</v>
@@ -1055,16 +1055,16 @@
         <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
         <v>5.55</v>
@@ -1156,7 +1156,7 @@
         <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="T6" t="n">
         <v>4.25</v>
@@ -1171,7 +1171,7 @@
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y6" t="n">
         <v>1.65</v>
@@ -1186,16 +1186,16 @@
         <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
         <v>1.35</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.29</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>2.71</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>3.38</v>
+        <v>7.92</v>
       </c>
       <c r="O8" t="n">
         <v>3.24</v>
@@ -1415,13 +1415,13 @@
         <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
         <v>6.55</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>4.45</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>6.3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>6.3</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1739,16 +1739,16 @@
         <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="P11" t="n">
         <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.87</v>
+        <v>6.99</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
         <v>2.28</v>
@@ -1760,13 +1760,13 @@
         <v>1.23</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
         <v>1.5</v>
@@ -1781,22 +1781,22 @@
         <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46016.64583333334</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N2" t="n">
-        <v>3.67</v>
+        <v>4.08</v>
       </c>
       <c r="O2" t="n">
         <v>2.87</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -787,64 +787,64 @@
         <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>4.06</v>
+        <v>3.84</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.05</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
         <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.74</v>
@@ -936,16 +936,16 @@
         <v>1.16</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
@@ -954,16 +954,16 @@
         <v>1.03</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG4" t="n">
         <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>
@@ -1019,19 +1019,19 @@
         <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.28</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.6</v>
@@ -1040,13 +1040,13 @@
         <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1055,34 +1055,34 @@
         <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.55</v>
+        <v>5.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46016.41666666666</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
         <v>4.22</v>
@@ -1156,7 +1156,7 @@
         <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
         <v>4.25</v>
@@ -1171,31 +1171,31 @@
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
         <v>6.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
         <v>1.35</v>
@@ -1257,10 +1257,10 @@
         <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>2.43</v>
@@ -1269,7 +1269,7 @@
         <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -1293,16 +1293,16 @@
         <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC7" t="n">
         <v>3.42</v>
@@ -1311,10 +1311,10 @@
         <v>1.23</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
         <v>1.24</v>
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>2.28</v>
       </c>
       <c r="M8" t="n">
-        <v>3.32</v>
+        <v>2.72</v>
       </c>
       <c r="N8" t="n">
-        <v>7.92</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.52</v>
+        <v>4.33</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
         <v>10</v>
@@ -1415,31 +1415,31 @@
         <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.47</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46016.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="N9" t="n">
-        <v>6.3</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.9</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="O11" t="n">
         <v>2.28</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.99</v>
+        <v>6.62</v>
       </c>
       <c r="R11" t="n">
         <v>1.46</v>
@@ -1754,10 +1754,10 @@
         <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="V11" t="n">
         <v>9.5</v>
@@ -1769,22 +1769,22 @@
         <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC11" t="n">
         <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE11" t="n">
         <v>2.34</v>
@@ -1796,7 +1796,7 @@
         <v>1.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46016.64583333334</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="M2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>2.87</v>
@@ -698,16 +698,16 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.3</v>
       </c>
       <c r="O4" t="n">
         <v>3.28</v>
@@ -936,16 +936,16 @@
         <v>1.16</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>2.66</v>
@@ -1055,16 +1055,16 @@
         <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
         <v>5.35</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>4.22</v>
@@ -1174,16 +1174,16 @@
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
         <v>6.1</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
@@ -1415,13 +1415,13 @@
         <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
         <v>6.4</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.9</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
         <v>2.28</v>
@@ -1769,16 +1769,16 @@
         <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
         <v>4.75</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.06</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.84</v>
+        <v>3.28</v>
       </c>
       <c r="P3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.03</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.84</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="T4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.56</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.28</v>
+        <v>3.84</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.56</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06</v>
+        <v>2.65</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.84</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.03</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.375</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -662,10 +662,10 @@
         <v>1.95</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2.87</v>
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="M3" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O3" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
         <v>3.5</v>
@@ -808,43 +808,43 @@
         <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W3" t="n">
         <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AC3" t="n">
         <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -906,28 +906,28 @@
         <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S4" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="T4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -948,19 +948,19 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.2</v>
+        <v>6.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AH4" t="n">
         <v>1.46</v>
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
         <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
         <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
         <v>9.199999999999999</v>
@@ -1052,13 +1052,13 @@
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
         <v>2.73</v>
@@ -1067,22 +1067,22 @@
         <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AF5" t="n">
         <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46016.41666666666</v>
@@ -1147,31 +1147,31 @@
         <v>4.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y6" t="n">
         <v>1.65</v>
@@ -1189,13 +1189,13 @@
         <v>6.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
         <v>1.35</v>
@@ -1254,67 +1254,67 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="O7" t="n">
         <v>2.43</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.7</v>
+        <v>4.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
         <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
         <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
         <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
         <v>1.24</v>
@@ -1382,19 +1382,19 @@
         <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P8" t="n">
         <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
         <v>4.15</v>
@@ -1403,7 +1403,7 @@
         <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
@@ -1412,7 +1412,7 @@
         <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z8" t="n">
         <v>2.1</v>
@@ -1424,10 +1424,10 @@
         <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
         <v>2.34</v>
@@ -1436,10 +1436,10 @@
         <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46016.5</v>
@@ -1492,28 +1492,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q9" t="n">
         <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
         <v>2.35</v>
@@ -1522,10 +1522,10 @@
         <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.04</v>
@@ -1534,31 +1534,31 @@
         <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.05</v>
+        <v>4.36</v>
       </c>
       <c r="AA9" t="n">
         <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
         <v>2.01</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1739,19 +1739,19 @@
         <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.62</v>
+        <v>7.21</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
         <v>3.34</v>
@@ -1760,13 +1760,13 @@
         <v>1.24</v>
       </c>
       <c r="V11" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
         <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
         <v>1.5</v>
@@ -1787,13 +1787,13 @@
         <v>1.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
         <v>2.08</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,76 +897,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.56</v>
+        <v>2.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.85</v>
+        <v>5.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46016.375</v>
+        <v>46016.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="T5" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="V5" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>3.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.2</v>
+        <v>6.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46016.41666666666</v>
+        <v>46016.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>2.95</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>2.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="O2" t="n">
         <v>2.87</v>
@@ -704,10 +704,10 @@
         <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N3" t="n">
         <v>2.32</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
         <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
         <v>3.5</v>
@@ -817,34 +817,34 @@
         <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AA3" t="n">
         <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46016.375</v>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.57</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="R4" t="n">
         <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
         <v>3.58</v>
@@ -939,31 +939,31 @@
         <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AD4" t="n">
         <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
         <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46016.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>4.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4</v>
+        <v>3.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="T5" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="U5" t="n">
         <v>1.14</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.56</v>
+        <v>3.27</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.85</v>
+        <v>6.1</v>
       </c>
       <c r="AD5" t="n">
         <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46016.45833333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>4.22</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.42</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="S6" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="T6" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U6" t="n">
         <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.1</v>
+        <v>6.85</v>
       </c>
       <c r="AD6" t="n">
         <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46016.45833333334</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
         <v>4.15</v>
@@ -1409,22 +1409,22 @@
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Z8" t="n">
         <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.09</v>
@@ -1436,7 +1436,7 @@
         <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
         <v>1.42</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.95</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>2.95</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>2.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>2.95</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>2.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1025,25 +1025,25 @@
         <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>4.22</v>
+        <v>4.61</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="S5" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="T5" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
         <v>9.800000000000001</v>
@@ -1052,7 +1052,7 @@
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
         <v>1.65</v>
@@ -1070,19 +1070,19 @@
         <v>6.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46016.45833333334</v>
@@ -1144,34 +1144,34 @@
         <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
         <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="T6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Y6" t="n">
         <v>1.83</v>
@@ -1186,22 +1186,22 @@
         <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.85</v>
+        <v>6.95</v>
       </c>
       <c r="AD6" t="n">
         <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.44</v>
       </c>
-      <c r="AG6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46016.45833333334</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AA8" t="n">
         <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="AD8" t="n">
         <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46016.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.95</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>2.95</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>2.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1739,34 +1739,34 @@
         <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.21</v>
+        <v>6.34</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
         <v>1.5</v>
@@ -1784,19 +1784,19 @@
         <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46016.64583333334</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.33</v>
       </c>
-      <c r="V7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46016.49305555555</v>
@@ -1356,20 +1356,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.36</v>
+        <v>4.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
         <v>3.5</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.34</v>
+        <v>6.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="T11" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46016.64583333334</v>

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">

--- a/jogos_2025-12-25.xlsx
+++ b/jogos_2025-12-25.xlsx
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>4.61</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.38</v>
+        <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="T5" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="V5" t="n">
-        <v>9.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.1</v>
+        <v>6.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46016.45833333334</v>
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>4.61</v>
       </c>
       <c r="P6" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>3.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="S6" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="T6" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.56</v>
+        <v>3.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.95</v>
+        <v>6.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46016.45833333334</v>
@@ -1466,20 +1466,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>2.97</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.61</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.1</v>
+        <v>2.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46016.60416666666</v>
@@ -1585,19 +1585,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.97</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.22</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46016.60416666666</v>
